--- a/Excel/PlayersStartConfig.xlsx
+++ b/Excel/PlayersStartConfig.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>战士</t>
+          <t>新手店主</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -537,11 +537,11 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"ingredient_carrot":"6","ingredient_salt":"3","ingredient_rice":"2","food_carrot_soup":"1"}</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>法师</t>
+          <t>料理学徒</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -563,11 +563,11 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"ingredient_mushroom":"3","ingredient_wheat":"3","ingredient_honey":"1"}</t>
         </is>
       </c>
     </row>
@@ -579,21 +579,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>盗贼</t>
+          <t>迷宫跑者</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"ingredient_carrot":"2","ingredient_salt":"2","ingredient_egg":"2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>END</t>
         </is>
       </c>
     </row>
